--- a/Data Files/12.1. Reverse Credit Transfer - Reverse Credit Transfer - Reverse Kredit Transfer Berhasil.xlsx
+++ b/Data Files/12.1. Reverse Credit Transfer - Reverse Credit Transfer - Reverse Kredit Transfer Berhasil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE4D6F8-D00F-47BE-AE35-F68C23672F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58000DB1-FF3A-4F0D-A7F0-44EFEA3C5C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25D99454-0DB0-4C8F-90AC-1BFA9B73EB2A}"/>
   </bookViews>
@@ -228,7 +228,7 @@
     <t>RltdEndToEndId</t>
   </si>
   <si>
-    <t>20250807FASTIDJA011361526</t>
+    <t>20250807FASTIDJA011361528</t>
   </si>
 </sst>
 </file>
@@ -315,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -324,7 +324,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -869,7 +868,7 @@
       <c r="AH2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AI2" s="1" t="s">
         <v>62</v>
       </c>
     </row>
